--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>135769040</v>
       </c>
       <c r="B11" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135768978</v>
       </c>
       <c r="B12" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135769001</v>
       </c>
       <c r="B13" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135769055</v>
       </c>
       <c r="B14" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135769080</v>
       </c>
       <c r="B15" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135769081</v>
       </c>
       <c r="B16" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135768987</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135769056</v>
       </c>
       <c r="B18" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135769067</v>
       </c>
       <c r="B19" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135769077</v>
       </c>
       <c r="B20" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135769083</v>
       </c>
       <c r="B21" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135769085</v>
       </c>
       <c r="B22" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135768986</v>
       </c>
       <c r="B23" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135768998</v>
       </c>
       <c r="B24" t="n">
-        <v>93339</v>
+        <v>93341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135768974</v>
       </c>
       <c r="B25" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135768975</v>
       </c>
       <c r="B26" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135768984</v>
       </c>
       <c r="B27" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>135769009</v>
       </c>
       <c r="B28" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>135769013</v>
       </c>
       <c r="B29" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>135769014</v>
       </c>
       <c r="B30" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135769024</v>
       </c>
       <c r="B31" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135769061</v>
       </c>
       <c r="B32" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135769062</v>
       </c>
       <c r="B33" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>135769068</v>
       </c>
       <c r="B34" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>135769004</v>
       </c>
       <c r="B73" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>135769042</v>
       </c>
       <c r="B74" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>135768992</v>
       </c>
       <c r="B75" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ99"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135768993</v>
+        <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476780</v>
+        <v>477020</v>
       </c>
       <c r="R2" t="n">
-        <v>6827880</v>
+        <v>6828242</v>
       </c>
       <c r="S2" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +769,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,13 +787,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768993</t>
+          <t>https://artportalen.se/Sighting/135801775</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135768997</v>
+        <v>135768993</v>
       </c>
       <c r="B3" t="n">
         <v>79473</v>
@@ -827,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476910</v>
+        <v>476780</v>
       </c>
       <c r="R3" t="n">
-        <v>6827873</v>
+        <v>6827880</v>
       </c>
       <c r="S3" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,13 +899,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768997</t>
+          <t>https://artportalen.se/Sighting/135768993</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135769026</v>
+        <v>135768997</v>
       </c>
       <c r="B4" t="n">
         <v>79473</v>
@@ -939,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476716</v>
+        <v>476910</v>
       </c>
       <c r="R4" t="n">
-        <v>6828615</v>
+        <v>6827873</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +975,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +985,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,13 +1011,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769026</t>
+          <t>https://artportalen.se/Sighting/135768997</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135769050</v>
+        <v>135769026</v>
       </c>
       <c r="B5" t="n">
         <v>79473</v>
@@ -1051,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477055</v>
+        <v>476716</v>
       </c>
       <c r="R5" t="n">
-        <v>6828259</v>
+        <v>6828615</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,13 +1123,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769050</t>
+          <t>https://artportalen.se/Sighting/135769026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135769057</v>
+        <v>135769050</v>
       </c>
       <c r="B6" t="n">
         <v>79473</v>
@@ -1163,13 +1164,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476856</v>
+        <v>477055</v>
       </c>
       <c r="R6" t="n">
-        <v>6828310</v>
+        <v>6828259</v>
       </c>
       <c r="S6" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,13 +1235,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769057</t>
+          <t>https://artportalen.se/Sighting/135769050</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135769060</v>
+        <v>135769057</v>
       </c>
       <c r="B7" t="n">
         <v>79473</v>
@@ -1275,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476730</v>
+        <v>476856</v>
       </c>
       <c r="R7" t="n">
-        <v>6828284</v>
+        <v>6828310</v>
       </c>
       <c r="S7" t="n">
         <v>38</v>
@@ -1310,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1347,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769060</t>
+          <t>https://artportalen.se/Sighting/135769057</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135769017</v>
+        <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>81423</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1364,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1388,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476860</v>
+        <v>476730</v>
       </c>
       <c r="R8" t="n">
-        <v>6828145</v>
+        <v>6828284</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,13 +1459,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769017</t>
+          <t>https://artportalen.se/Sighting/135769060</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135769031</v>
+        <v>135769017</v>
       </c>
       <c r="B9" t="n">
         <v>81423</v>
@@ -1499,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476879</v>
+        <v>476860</v>
       </c>
       <c r="R9" t="n">
-        <v>6828554</v>
+        <v>6828145</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,13 +1571,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769031</t>
+          <t>https://artportalen.se/Sighting/135769017</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135769041</v>
+        <v>135769031</v>
       </c>
       <c r="B10" t="n">
         <v>81423</v>
@@ -1611,13 +1612,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477009</v>
+        <v>476879</v>
       </c>
       <c r="R10" t="n">
-        <v>6828279</v>
+        <v>6828554</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1657,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,38 +1683,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769041</t>
+          <t>https://artportalen.se/Sighting/135769031</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135769040</v>
+        <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>81423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1724,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476997</v>
+        <v>477009</v>
       </c>
       <c r="R11" t="n">
-        <v>6828281</v>
+        <v>6828279</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,16 +1795,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769040</t>
+          <t>https://artportalen.se/Sighting/135769041</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135768978</v>
+        <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92229</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1812,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1836,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476551</v>
+        <v>476997</v>
       </c>
       <c r="R12" t="n">
-        <v>6828210</v>
+        <v>6828281</v>
       </c>
       <c r="S12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1871,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1881,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,13 +1907,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768978</t>
+          <t>https://artportalen.se/Sighting/135769040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135769001</v>
+        <v>135768978</v>
       </c>
       <c r="B13" t="n">
         <v>92229</v>
@@ -1947,13 +1948,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476891</v>
+        <v>476551</v>
       </c>
       <c r="R13" t="n">
-        <v>6827965</v>
+        <v>6828210</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1983,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1993,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,13 +2019,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769001</t>
+          <t>https://artportalen.se/Sighting/135768978</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135769055</v>
+        <v>135769001</v>
       </c>
       <c r="B14" t="n">
         <v>92229</v>
@@ -2059,13 +2060,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476870</v>
+        <v>476891</v>
       </c>
       <c r="R14" t="n">
-        <v>6828292</v>
+        <v>6827965</v>
       </c>
       <c r="S14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2095,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2105,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,13 +2131,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769055</t>
+          <t>https://artportalen.se/Sighting/135769001</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135769080</v>
+        <v>135769055</v>
       </c>
       <c r="B15" t="n">
         <v>92229</v>
@@ -2171,13 +2172,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476619</v>
+        <v>476870</v>
       </c>
       <c r="R15" t="n">
-        <v>6828576</v>
+        <v>6828292</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2207,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2217,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,13 +2243,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769080</t>
+          <t>https://artportalen.se/Sighting/135769055</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135769081</v>
+        <v>135769080</v>
       </c>
       <c r="B16" t="n">
         <v>92229</v>
@@ -2283,13 +2284,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476587</v>
+        <v>476619</v>
       </c>
       <c r="R16" t="n">
-        <v>6828396</v>
+        <v>6828576</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2319,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2329,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,38 +2355,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769081</t>
+          <t>https://artportalen.se/Sighting/135769080</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135768987</v>
+        <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92103</v>
+        <v>92229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2396,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476688</v>
+        <v>476587</v>
       </c>
       <c r="R17" t="n">
-        <v>6827976</v>
+        <v>6828396</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2431,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2441,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,13 +2467,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768987</t>
+          <t>https://artportalen.se/Sighting/135769081</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135769056</v>
+        <v>135768987</v>
       </c>
       <c r="B18" t="n">
         <v>92103</v>
@@ -2507,13 +2508,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476863</v>
+        <v>476688</v>
       </c>
       <c r="R18" t="n">
-        <v>6828287</v>
+        <v>6827976</v>
       </c>
       <c r="S18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2543,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2553,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,13 +2579,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769056</t>
+          <t>https://artportalen.se/Sighting/135768987</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135769067</v>
+        <v>135769056</v>
       </c>
       <c r="B19" t="n">
         <v>92103</v>
@@ -2619,13 +2620,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476648</v>
+        <v>476863</v>
       </c>
       <c r="R19" t="n">
-        <v>6828343</v>
+        <v>6828287</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,7 +2655,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2665,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,13 +2691,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769067</t>
+          <t>https://artportalen.se/Sighting/135769056</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135769077</v>
+        <v>135769067</v>
       </c>
       <c r="B20" t="n">
         <v>92103</v>
@@ -2731,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476707</v>
+        <v>476648</v>
       </c>
       <c r="R20" t="n">
-        <v>6828552</v>
+        <v>6828343</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2767,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2777,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,13 +2803,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769077</t>
+          <t>https://artportalen.se/Sighting/135769067</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135769083</v>
+        <v>135769077</v>
       </c>
       <c r="B21" t="n">
         <v>92103</v>
@@ -2843,13 +2844,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476581</v>
+        <v>476707</v>
       </c>
       <c r="R21" t="n">
-        <v>6828401</v>
+        <v>6828552</v>
       </c>
       <c r="S21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2879,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2889,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2914,13 +2915,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769083</t>
+          <t>https://artportalen.se/Sighting/135769077</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135769085</v>
+        <v>135769083</v>
       </c>
       <c r="B22" t="n">
         <v>92103</v>
@@ -2955,13 +2956,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476606</v>
+        <v>476581</v>
       </c>
       <c r="R22" t="n">
-        <v>6828344</v>
+        <v>6828401</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,16 +3027,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769085</t>
+          <t>https://artportalen.se/Sighting/135769083</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135768986</v>
+        <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>91972</v>
+        <v>92103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,21 +3044,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,13 +3068,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476688</v>
+        <v>476606</v>
       </c>
       <c r="R23" t="n">
-        <v>6827976</v>
+        <v>6828344</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3103,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3113,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3138,16 +3139,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768986</t>
+          <t>https://artportalen.se/Sighting/135769085</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135768998</v>
+        <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>93341</v>
+        <v>91972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,21 +3156,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>3242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,13 +3180,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476880</v>
+        <v>476688</v>
       </c>
       <c r="R24" t="n">
-        <v>6827829</v>
+        <v>6827976</v>
       </c>
       <c r="S24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3215,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3225,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,16 +3251,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768998</t>
+          <t>https://artportalen.se/Sighting/135768986</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135768974</v>
+        <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93347</v>
+        <v>93341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +3268,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,13 +3292,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476709</v>
+        <v>476880</v>
       </c>
       <c r="R25" t="n">
-        <v>6828205</v>
+        <v>6827829</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3327,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3337,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,13 +3363,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768974</t>
+          <t>https://artportalen.se/Sighting/135768998</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135768975</v>
+        <v>135768974</v>
       </c>
       <c r="B26" t="n">
         <v>93347</v>
@@ -3403,13 +3404,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476706</v>
+        <v>476709</v>
       </c>
       <c r="R26" t="n">
-        <v>6828208</v>
+        <v>6828205</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3474,13 +3475,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768975</t>
+          <t>https://artportalen.se/Sighting/135768974</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135768984</v>
+        <v>135768975</v>
       </c>
       <c r="B27" t="n">
         <v>93347</v>
@@ -3515,13 +3516,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476675</v>
+        <v>476706</v>
       </c>
       <c r="R27" t="n">
-        <v>6828013</v>
+        <v>6828208</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,7 +3551,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3561,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,13 +3587,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768984</t>
+          <t>https://artportalen.se/Sighting/135768975</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135769009</v>
+        <v>135768984</v>
       </c>
       <c r="B28" t="n">
         <v>93347</v>
@@ -3627,13 +3628,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476810</v>
+        <v>476675</v>
       </c>
       <c r="R28" t="n">
-        <v>6828009</v>
+        <v>6828013</v>
       </c>
       <c r="S28" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3662,7 +3663,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3673,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,13 +3699,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769009</t>
+          <t>https://artportalen.se/Sighting/135768984</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135769013</v>
+        <v>135769009</v>
       </c>
       <c r="B29" t="n">
         <v>93347</v>
@@ -3739,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476750</v>
+        <v>476810</v>
       </c>
       <c r="R29" t="n">
-        <v>6828142</v>
+        <v>6828009</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3774,7 +3775,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3785,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,13 +3811,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769013</t>
+          <t>https://artportalen.se/Sighting/135769009</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135769014</v>
+        <v>135769013</v>
       </c>
       <c r="B30" t="n">
         <v>93347</v>
@@ -3851,13 +3852,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476833</v>
+        <v>476750</v>
       </c>
       <c r="R30" t="n">
-        <v>6828182</v>
+        <v>6828142</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3886,7 +3887,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3897,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3922,13 +3923,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769014</t>
+          <t>https://artportalen.se/Sighting/135769013</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135769024</v>
+        <v>135769014</v>
       </c>
       <c r="B31" t="n">
         <v>93347</v>
@@ -3963,13 +3964,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476682</v>
+        <v>476833</v>
       </c>
       <c r="R31" t="n">
-        <v>6828614</v>
+        <v>6828182</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3998,7 +3999,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +4009,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4034,13 +4035,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769024</t>
+          <t>https://artportalen.se/Sighting/135769014</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135769061</v>
+        <v>135769024</v>
       </c>
       <c r="B32" t="n">
         <v>93347</v>
@@ -4075,13 +4076,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476716</v>
+        <v>476682</v>
       </c>
       <c r="R32" t="n">
-        <v>6828275</v>
+        <v>6828614</v>
       </c>
       <c r="S32" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,7 +4111,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4121,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4146,13 +4147,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769061</t>
+          <t>https://artportalen.se/Sighting/135769024</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135769062</v>
+        <v>135769061</v>
       </c>
       <c r="B33" t="n">
         <v>93347</v>
@@ -4187,13 +4188,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476705</v>
+        <v>476716</v>
       </c>
       <c r="R33" t="n">
         <v>6828275</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4258,38 +4259,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769062</t>
+          <t>https://artportalen.se/Sighting/135769061</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135769068</v>
+        <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93351</v>
+        <v>93347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,13 +4300,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476702</v>
+        <v>476705</v>
       </c>
       <c r="R34" t="n">
-        <v>6828321</v>
+        <v>6828275</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4334,7 +4335,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4344,7 +4345,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4353,7 +4354,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4371,16 +4371,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769068</t>
+          <t>https://artportalen.se/Sighting/135769062</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135768973</v>
+        <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>93351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4388,21 +4388,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476739</v>
+        <v>476702</v>
       </c>
       <c r="R35" t="n">
-        <v>6828218</v>
+        <v>6828321</v>
       </c>
       <c r="S35" t="n">
         <v>11</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4466,6 +4466,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4483,13 +4484,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768973</t>
+          <t>https://artportalen.se/Sighting/135769068</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135768979</v>
+        <v>135768973</v>
       </c>
       <c r="B36" t="n">
         <v>79441</v>
@@ -4524,13 +4525,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476582</v>
+        <v>476739</v>
       </c>
       <c r="R36" t="n">
-        <v>6828281</v>
+        <v>6828218</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4559,7 +4560,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4569,7 +4570,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,13 +4596,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768979</t>
+          <t>https://artportalen.se/Sighting/135768973</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135769003</v>
+        <v>135768979</v>
       </c>
       <c r="B37" t="n">
         <v>79441</v>
@@ -4636,13 +4637,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476887</v>
+        <v>476582</v>
       </c>
       <c r="R37" t="n">
-        <v>6827982</v>
+        <v>6828281</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4671,7 +4672,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4681,7 +4682,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,13 +4708,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769003</t>
+          <t>https://artportalen.se/Sighting/135768979</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135769023</v>
+        <v>135769003</v>
       </c>
       <c r="B38" t="n">
         <v>79441</v>
@@ -4748,13 +4749,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476676</v>
+        <v>476887</v>
       </c>
       <c r="R38" t="n">
-        <v>6828636</v>
+        <v>6827982</v>
       </c>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4783,7 +4784,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4793,7 +4794,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,13 +4820,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769023</t>
+          <t>https://artportalen.se/Sighting/135769003</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135769036</v>
+        <v>135769023</v>
       </c>
       <c r="B39" t="n">
         <v>79441</v>
@@ -4860,13 +4861,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476914</v>
+        <v>476676</v>
       </c>
       <c r="R39" t="n">
-        <v>6828370</v>
+        <v>6828636</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4895,7 +4896,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4905,7 +4906,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4931,13 +4932,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769036</t>
+          <t>https://artportalen.se/Sighting/135769023</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135769043</v>
+        <v>135769036</v>
       </c>
       <c r="B40" t="n">
         <v>79441</v>
@@ -4972,13 +4973,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477039</v>
+        <v>476914</v>
       </c>
       <c r="R40" t="n">
-        <v>6828305</v>
+        <v>6828370</v>
       </c>
       <c r="S40" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5007,7 +5008,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5017,7 +5018,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,13 +5044,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769043</t>
+          <t>https://artportalen.se/Sighting/135769036</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135769045</v>
+        <v>135769043</v>
       </c>
       <c r="B41" t="n">
         <v>79441</v>
@@ -5084,13 +5085,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477087</v>
+        <v>477039</v>
       </c>
       <c r="R41" t="n">
-        <v>6828327</v>
+        <v>6828305</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5119,7 +5120,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5129,7 +5130,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,13 +5156,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769045</t>
+          <t>https://artportalen.se/Sighting/135769043</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135769051</v>
+        <v>135769045</v>
       </c>
       <c r="B42" t="n">
         <v>79441</v>
@@ -5196,13 +5197,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477037</v>
+        <v>477087</v>
       </c>
       <c r="R42" t="n">
-        <v>6828241</v>
+        <v>6828327</v>
       </c>
       <c r="S42" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5231,7 +5232,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5241,7 +5242,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,13 +5268,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769051</t>
+          <t>https://artportalen.se/Sighting/135769045</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135769053</v>
+        <v>135769051</v>
       </c>
       <c r="B43" t="n">
         <v>79441</v>
@@ -5308,13 +5309,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476925</v>
+        <v>477037</v>
       </c>
       <c r="R43" t="n">
-        <v>6828272</v>
+        <v>6828241</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5344,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5353,7 +5354,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,38 +5380,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769053</t>
+          <t>https://artportalen.se/Sighting/135769051</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135769006</v>
+        <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79465</v>
+        <v>79441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5420,13 +5421,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476861</v>
+        <v>476925</v>
       </c>
       <c r="R44" t="n">
-        <v>6828091</v>
+        <v>6828272</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5455,7 +5456,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5465,7 +5466,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,13 +5492,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769006</t>
+          <t>https://artportalen.se/Sighting/135769053</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135769073</v>
+        <v>135769006</v>
       </c>
       <c r="B45" t="n">
         <v>79465</v>
@@ -5532,10 +5533,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476655</v>
+        <v>476861</v>
       </c>
       <c r="R45" t="n">
-        <v>6828480</v>
+        <v>6828091</v>
       </c>
       <c r="S45" t="n">
         <v>8</v>
@@ -5567,7 +5568,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5577,7 +5578,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,38 +5604,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769073</t>
+          <t>https://artportalen.se/Sighting/135769006</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135768991</v>
+        <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>78844</v>
+        <v>79465</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5644,13 +5645,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476727</v>
+        <v>476655</v>
       </c>
       <c r="R46" t="n">
-        <v>6827957</v>
+        <v>6828480</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5679,7 +5680,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5689,7 +5690,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5715,13 +5716,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768991</t>
+          <t>https://artportalen.se/Sighting/135769073</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135769000</v>
+        <v>135768991</v>
       </c>
       <c r="B47" t="n">
         <v>78844</v>
@@ -5756,13 +5757,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476885</v>
+        <v>476727</v>
       </c>
       <c r="R47" t="n">
-        <v>6827946</v>
+        <v>6827957</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5791,7 +5792,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5801,7 +5802,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5827,13 +5828,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769000</t>
+          <t>https://artportalen.se/Sighting/135768991</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135769005</v>
+        <v>135769000</v>
       </c>
       <c r="B48" t="n">
         <v>78844</v>
@@ -5868,13 +5869,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476856</v>
+        <v>476885</v>
       </c>
       <c r="R48" t="n">
-        <v>6828026</v>
+        <v>6827946</v>
       </c>
       <c r="S48" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5903,7 +5904,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5913,7 +5914,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,13 +5940,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769005</t>
+          <t>https://artportalen.se/Sighting/135769000</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135769016</v>
+        <v>135769005</v>
       </c>
       <c r="B49" t="n">
         <v>78844</v>
@@ -5980,13 +5981,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476854</v>
+        <v>476856</v>
       </c>
       <c r="R49" t="n">
-        <v>6828144</v>
+        <v>6828026</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6015,7 +6016,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6025,7 +6026,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6051,13 +6052,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769016</t>
+          <t>https://artportalen.se/Sighting/135769005</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135769029</v>
+        <v>135769016</v>
       </c>
       <c r="B50" t="n">
         <v>78844</v>
@@ -6092,13 +6093,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476757</v>
+        <v>476854</v>
       </c>
       <c r="R50" t="n">
-        <v>6828581</v>
+        <v>6828144</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6127,7 +6128,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6137,7 +6138,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6163,13 +6164,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769029</t>
+          <t>https://artportalen.se/Sighting/135769016</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135769030</v>
+        <v>135769029</v>
       </c>
       <c r="B51" t="n">
         <v>78844</v>
@@ -6204,13 +6205,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476813</v>
+        <v>476757</v>
       </c>
       <c r="R51" t="n">
-        <v>6828634</v>
+        <v>6828581</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6239,7 +6240,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6249,7 +6250,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6275,13 +6276,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769030</t>
+          <t>https://artportalen.se/Sighting/135769029</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135769033</v>
+        <v>135769030</v>
       </c>
       <c r="B52" t="n">
         <v>78844</v>
@@ -6316,13 +6317,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476907</v>
+        <v>476813</v>
       </c>
       <c r="R52" t="n">
-        <v>6828447</v>
+        <v>6828634</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6351,7 +6352,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6361,7 +6362,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6387,13 +6388,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769033</t>
+          <t>https://artportalen.se/Sighting/135769030</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135769035</v>
+        <v>135769033</v>
       </c>
       <c r="B53" t="n">
         <v>78844</v>
@@ -6428,13 +6429,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476927</v>
+        <v>476907</v>
       </c>
       <c r="R53" t="n">
-        <v>6828385</v>
+        <v>6828447</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6463,7 +6464,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6473,7 +6474,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6499,13 +6500,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769035</t>
+          <t>https://artportalen.se/Sighting/135769033</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135769066</v>
+        <v>135769035</v>
       </c>
       <c r="B54" t="n">
         <v>78844</v>
@@ -6540,13 +6541,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476628</v>
+        <v>476927</v>
       </c>
       <c r="R54" t="n">
-        <v>6828300</v>
+        <v>6828385</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6575,7 +6576,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6585,7 +6586,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6611,16 +6612,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769066</t>
+          <t>https://artportalen.se/Sighting/135769035</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135768990</v>
+        <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>79198</v>
+        <v>78844</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6628,21 +6629,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6652,13 +6653,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476707</v>
+        <v>476628</v>
       </c>
       <c r="R55" t="n">
-        <v>6827964</v>
+        <v>6828300</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6687,7 +6688,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6697,7 +6698,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6723,13 +6724,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768990</t>
+          <t>https://artportalen.se/Sighting/135769066</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135769015</v>
+        <v>135768990</v>
       </c>
       <c r="B56" t="n">
         <v>79198</v>
@@ -6764,10 +6765,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476849</v>
+        <v>476707</v>
       </c>
       <c r="R56" t="n">
-        <v>6828138</v>
+        <v>6827964</v>
       </c>
       <c r="S56" t="n">
         <v>12</v>
@@ -6799,7 +6800,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6809,7 +6810,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6835,16 +6836,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769015</t>
+          <t>https://artportalen.se/Sighting/135768990</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135769002</v>
+        <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>80060</v>
+        <v>79198</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6852,21 +6853,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6876,13 +6877,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476887</v>
+        <v>476849</v>
       </c>
       <c r="R57" t="n">
-        <v>6827982</v>
+        <v>6828138</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6911,7 +6912,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6921,7 +6922,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6947,13 +6948,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769002</t>
+          <t>https://artportalen.se/Sighting/135769015</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135769007</v>
+        <v>135769002</v>
       </c>
       <c r="B58" t="n">
         <v>80060</v>
@@ -6988,13 +6989,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476777</v>
+        <v>476887</v>
       </c>
       <c r="R58" t="n">
-        <v>6828032</v>
+        <v>6827982</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7023,7 +7024,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7033,7 +7034,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7059,13 +7060,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769007</t>
+          <t>https://artportalen.se/Sighting/135769002</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135769021</v>
+        <v>135769007</v>
       </c>
       <c r="B59" t="n">
         <v>80060</v>
@@ -7100,13 +7101,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476864</v>
+        <v>476777</v>
       </c>
       <c r="R59" t="n">
-        <v>6828186</v>
+        <v>6828032</v>
       </c>
       <c r="S59" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7135,7 +7136,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7145,7 +7146,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7171,13 +7172,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769021</t>
+          <t>https://artportalen.se/Sighting/135769007</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135769022</v>
+        <v>135769021</v>
       </c>
       <c r="B60" t="n">
         <v>80060</v>
@@ -7212,13 +7213,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476822</v>
+        <v>476864</v>
       </c>
       <c r="R60" t="n">
-        <v>6828228</v>
+        <v>6828186</v>
       </c>
       <c r="S60" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7247,7 +7248,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7257,7 +7258,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7283,13 +7284,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769022</t>
+          <t>https://artportalen.se/Sighting/135769021</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135769027</v>
+        <v>135769022</v>
       </c>
       <c r="B61" t="n">
         <v>80060</v>
@@ -7324,13 +7325,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476737</v>
+        <v>476822</v>
       </c>
       <c r="R61" t="n">
-        <v>6828614</v>
+        <v>6828228</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7359,7 +7360,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7369,7 +7370,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7395,13 +7396,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769027</t>
+          <t>https://artportalen.se/Sighting/135769022</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135769037</v>
+        <v>135769027</v>
       </c>
       <c r="B62" t="n">
         <v>80060</v>
@@ -7436,13 +7437,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476914</v>
+        <v>476737</v>
       </c>
       <c r="R62" t="n">
-        <v>6828350</v>
+        <v>6828614</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7471,7 +7472,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7481,7 +7482,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7507,13 +7508,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769037</t>
+          <t>https://artportalen.se/Sighting/135769027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135769047</v>
+        <v>135769037</v>
       </c>
       <c r="B63" t="n">
         <v>80060</v>
@@ -7548,13 +7549,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>477083</v>
+        <v>476914</v>
       </c>
       <c r="R63" t="n">
-        <v>6828378</v>
+        <v>6828350</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7583,7 +7584,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7593,7 +7594,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7619,13 +7620,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769047</t>
+          <t>https://artportalen.se/Sighting/135769037</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135769058</v>
+        <v>135769047</v>
       </c>
       <c r="B64" t="n">
         <v>80060</v>
@@ -7660,13 +7661,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476737</v>
+        <v>477083</v>
       </c>
       <c r="R64" t="n">
-        <v>6828294</v>
+        <v>6828378</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7695,7 +7696,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7705,7 +7706,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7731,13 +7732,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769058</t>
+          <t>https://artportalen.se/Sighting/135769047</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135769071</v>
+        <v>135769058</v>
       </c>
       <c r="B65" t="n">
         <v>80060</v>
@@ -7772,13 +7773,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476704</v>
+        <v>476737</v>
       </c>
       <c r="R65" t="n">
-        <v>6828363</v>
+        <v>6828294</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7807,7 +7808,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7817,7 +7818,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7843,13 +7844,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769071</t>
+          <t>https://artportalen.se/Sighting/135769058</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135769076</v>
+        <v>135769071</v>
       </c>
       <c r="B66" t="n">
         <v>80060</v>
@@ -7884,13 +7885,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476689</v>
+        <v>476704</v>
       </c>
       <c r="R66" t="n">
-        <v>6828490</v>
+        <v>6828363</v>
       </c>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7919,7 +7920,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7929,7 +7930,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7955,16 +7956,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769076</t>
+          <t>https://artportalen.se/Sighting/135769071</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135769032</v>
+        <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>78445</v>
+        <v>80060</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7972,21 +7973,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7996,13 +7997,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476906</v>
+        <v>476689</v>
       </c>
       <c r="R67" t="n">
-        <v>6828445</v>
+        <v>6828490</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8031,7 +8032,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8041,7 +8042,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8067,13 +8068,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769032</t>
+          <t>https://artportalen.se/Sighting/135769076</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135769039</v>
+        <v>135769032</v>
       </c>
       <c r="B68" t="n">
         <v>78445</v>
@@ -8108,13 +8109,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476914</v>
+        <v>476906</v>
       </c>
       <c r="R68" t="n">
-        <v>6828350</v>
+        <v>6828445</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8143,7 +8144,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8153,7 +8154,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8179,16 +8180,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769039</t>
+          <t>https://artportalen.se/Sighting/135769032</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135769010</v>
+        <v>135769039</v>
       </c>
       <c r="B69" t="n">
-        <v>57980</v>
+        <v>78445</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8196,39 +8197,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lilla atjomäck, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476720</v>
+        <v>476914</v>
       </c>
       <c r="R69" t="n">
-        <v>6828070</v>
+        <v>6828350</v>
       </c>
       <c r="S69" t="n">
         <v>9</v>
@@ -8260,7 +8256,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8270,7 +8266,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8296,44 +8292,44 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769010</t>
+          <t>https://artportalen.se/Sighting/135769039</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135769011</v>
+        <v>135769010</v>
       </c>
       <c r="B70" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8342,13 +8338,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476722</v>
+        <v>476720</v>
       </c>
       <c r="R70" t="n">
-        <v>6828166</v>
+        <v>6828070</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8377,7 +8373,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8387,7 +8383,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8413,44 +8409,44 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769011</t>
+          <t>https://artportalen.se/Sighting/135769010</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135769052</v>
+        <v>135769011</v>
       </c>
       <c r="B71" t="n">
-        <v>5180</v>
+        <v>57167</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8459,13 +8455,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>477011</v>
+        <v>476722</v>
       </c>
       <c r="R71" t="n">
-        <v>6828245</v>
+        <v>6828166</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8494,7 +8490,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8504,7 +8500,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8530,16 +8526,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769052</t>
+          <t>https://artportalen.se/Sighting/135769011</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135769078</v>
+        <v>135769052</v>
       </c>
       <c r="B72" t="n">
-        <v>58141</v>
+        <v>5180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8547,37 +8543,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lilla atjomäck, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476724</v>
+        <v>477011</v>
       </c>
       <c r="R72" t="n">
-        <v>6828863</v>
+        <v>6828245</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8606,7 +8607,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8616,7 +8617,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8642,38 +8643,38 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769078</t>
+          <t>https://artportalen.se/Sighting/135769052</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135769004</v>
+        <v>135769078</v>
       </c>
       <c r="B73" t="n">
-        <v>98144</v>
+        <v>58141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8683,13 +8684,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476877</v>
+        <v>476724</v>
       </c>
       <c r="R73" t="n">
-        <v>6827984</v>
+        <v>6828863</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8718,7 +8719,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8728,7 +8729,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8754,13 +8755,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769004</t>
+          <t>https://artportalen.se/Sighting/135769078</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135769042</v>
+        <v>135769004</v>
       </c>
       <c r="B74" t="n">
         <v>98144</v>
@@ -8795,13 +8796,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>477009</v>
+        <v>476877</v>
       </c>
       <c r="R74" t="n">
-        <v>6828275</v>
+        <v>6827984</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8830,7 +8831,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8840,7 +8841,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8866,16 +8867,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769042</t>
+          <t>https://artportalen.se/Sighting/135769004</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135768992</v>
+        <v>135769042</v>
       </c>
       <c r="B75" t="n">
-        <v>98138</v>
+        <v>98144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8883,16 +8884,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8907,13 +8908,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476723</v>
+        <v>477009</v>
       </c>
       <c r="R75" t="n">
-        <v>6827952</v>
+        <v>6828275</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8942,7 +8943,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8952,7 +8953,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8978,38 +8979,38 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768992</t>
+          <t>https://artportalen.se/Sighting/135769042</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135768980</v>
+        <v>135768992</v>
       </c>
       <c r="B76" t="n">
-        <v>79199</v>
+        <v>98138</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9019,13 +9020,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476631</v>
+        <v>476723</v>
       </c>
       <c r="R76" t="n">
-        <v>6828169</v>
+        <v>6827952</v>
       </c>
       <c r="S76" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9054,7 +9055,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9064,7 +9065,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9090,13 +9091,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768980</t>
+          <t>https://artportalen.se/Sighting/135768992</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135768983</v>
+        <v>135768980</v>
       </c>
       <c r="B77" t="n">
         <v>79199</v>
@@ -9131,10 +9132,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476635</v>
+        <v>476631</v>
       </c>
       <c r="R77" t="n">
-        <v>6828068</v>
+        <v>6828169</v>
       </c>
       <c r="S77" t="n">
         <v>26</v>
@@ -9166,7 +9167,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9176,7 +9177,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9202,13 +9203,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768983</t>
+          <t>https://artportalen.se/Sighting/135768980</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135768985</v>
+        <v>135768983</v>
       </c>
       <c r="B78" t="n">
         <v>79199</v>
@@ -9243,13 +9244,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476662</v>
+        <v>476635</v>
       </c>
       <c r="R78" t="n">
-        <v>6827985</v>
+        <v>6828068</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9278,7 +9279,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9288,7 +9289,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9314,13 +9315,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768985</t>
+          <t>https://artportalen.se/Sighting/135768983</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135768989</v>
+        <v>135768985</v>
       </c>
       <c r="B79" t="n">
         <v>79199</v>
@@ -9355,13 +9356,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476706</v>
+        <v>476662</v>
       </c>
       <c r="R79" t="n">
-        <v>6827964</v>
+        <v>6827985</v>
       </c>
       <c r="S79" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9390,7 +9391,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9400,7 +9401,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9426,13 +9427,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768989</t>
+          <t>https://artportalen.se/Sighting/135768985</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135768995</v>
+        <v>135768989</v>
       </c>
       <c r="B80" t="n">
         <v>79199</v>
@@ -9467,13 +9468,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476840</v>
+        <v>476706</v>
       </c>
       <c r="R80" t="n">
-        <v>6827894</v>
+        <v>6827964</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9502,7 +9503,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9512,7 +9513,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9538,13 +9539,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768995</t>
+          <t>https://artportalen.se/Sighting/135768989</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135768999</v>
+        <v>135768995</v>
       </c>
       <c r="B81" t="n">
         <v>79199</v>
@@ -9579,13 +9580,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476881</v>
+        <v>476840</v>
       </c>
       <c r="R81" t="n">
-        <v>6827947</v>
+        <v>6827894</v>
       </c>
       <c r="S81" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9614,7 +9615,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9624,7 +9625,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9650,13 +9651,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768999</t>
+          <t>https://artportalen.se/Sighting/135768995</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135769008</v>
+        <v>135768999</v>
       </c>
       <c r="B82" t="n">
         <v>79199</v>
@@ -9691,13 +9692,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476776</v>
+        <v>476881</v>
       </c>
       <c r="R82" t="n">
-        <v>6828033</v>
+        <v>6827947</v>
       </c>
       <c r="S82" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9726,7 +9727,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9736,7 +9737,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9762,13 +9763,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769008</t>
+          <t>https://artportalen.se/Sighting/135768999</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135769019</v>
+        <v>135769008</v>
       </c>
       <c r="B83" t="n">
         <v>79199</v>
@@ -9803,13 +9804,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476864</v>
+        <v>476776</v>
       </c>
       <c r="R83" t="n">
-        <v>6828186</v>
+        <v>6828033</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9838,7 +9839,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9848,7 +9849,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9874,13 +9875,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769019</t>
+          <t>https://artportalen.se/Sighting/135769008</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135769025</v>
+        <v>135769019</v>
       </c>
       <c r="B84" t="n">
         <v>79199</v>
@@ -9915,13 +9916,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476708</v>
+        <v>476864</v>
       </c>
       <c r="R84" t="n">
-        <v>6828618</v>
+        <v>6828186</v>
       </c>
       <c r="S84" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9950,7 +9951,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9960,7 +9961,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9986,13 +9987,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769025</t>
+          <t>https://artportalen.se/Sighting/135769019</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135769028</v>
+        <v>135769025</v>
       </c>
       <c r="B85" t="n">
         <v>79199</v>
@@ -10027,13 +10028,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476743</v>
+        <v>476708</v>
       </c>
       <c r="R85" t="n">
-        <v>6828616</v>
+        <v>6828618</v>
       </c>
       <c r="S85" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10062,7 +10063,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10072,7 +10073,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10098,13 +10099,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769028</t>
+          <t>https://artportalen.se/Sighting/135769025</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135769046</v>
+        <v>135769028</v>
       </c>
       <c r="B86" t="n">
         <v>79199</v>
@@ -10139,13 +10140,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>477084</v>
+        <v>476743</v>
       </c>
       <c r="R86" t="n">
-        <v>6828344</v>
+        <v>6828616</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10174,7 +10175,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10184,7 +10185,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10210,13 +10211,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769046</t>
+          <t>https://artportalen.se/Sighting/135769028</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135769048</v>
+        <v>135769046</v>
       </c>
       <c r="B87" t="n">
         <v>79199</v>
@@ -10251,13 +10252,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477083</v>
+        <v>477084</v>
       </c>
       <c r="R87" t="n">
-        <v>6828378</v>
+        <v>6828344</v>
       </c>
       <c r="S87" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10322,13 +10323,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769048</t>
+          <t>https://artportalen.se/Sighting/135769046</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135769059</v>
+        <v>135769048</v>
       </c>
       <c r="B88" t="n">
         <v>79199</v>
@@ -10363,13 +10364,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476732</v>
+        <v>477083</v>
       </c>
       <c r="R88" t="n">
-        <v>6828298</v>
+        <v>6828378</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10398,7 +10399,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10408,7 +10409,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10434,13 +10435,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769059</t>
+          <t>https://artportalen.se/Sighting/135769048</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135769063</v>
+        <v>135769059</v>
       </c>
       <c r="B89" t="n">
         <v>79199</v>
@@ -10475,13 +10476,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476661</v>
+        <v>476732</v>
       </c>
       <c r="R89" t="n">
-        <v>6828289</v>
+        <v>6828298</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10510,7 +10511,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10520,7 +10521,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10546,13 +10547,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769063</t>
+          <t>https://artportalen.se/Sighting/135769059</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135769064</v>
+        <v>135769063</v>
       </c>
       <c r="B90" t="n">
         <v>79199</v>
@@ -10587,13 +10588,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476627</v>
+        <v>476661</v>
       </c>
       <c r="R90" t="n">
-        <v>6828296</v>
+        <v>6828289</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10622,7 +10623,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10632,7 +10633,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10658,13 +10659,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769064</t>
+          <t>https://artportalen.se/Sighting/135769063</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135769070</v>
+        <v>135769064</v>
       </c>
       <c r="B91" t="n">
         <v>79199</v>
@@ -10699,13 +10700,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476703</v>
+        <v>476627</v>
       </c>
       <c r="R91" t="n">
-        <v>6828355</v>
+        <v>6828296</v>
       </c>
       <c r="S91" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10734,7 +10735,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10744,7 +10745,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10770,16 +10771,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769070</t>
+          <t>https://artportalen.se/Sighting/135769064</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135768977</v>
+        <v>135769070</v>
       </c>
       <c r="B92" t="n">
-        <v>80031</v>
+        <v>79199</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10787,21 +10788,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10811,13 +10812,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476559</v>
+        <v>476703</v>
       </c>
       <c r="R92" t="n">
-        <v>6828201</v>
+        <v>6828355</v>
       </c>
       <c r="S92" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10846,7 +10847,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10856,7 +10857,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10882,13 +10883,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768977</t>
+          <t>https://artportalen.se/Sighting/135769070</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135768982</v>
+        <v>135768977</v>
       </c>
       <c r="B93" t="n">
         <v>80031</v>
@@ -10923,10 +10924,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476637</v>
+        <v>476559</v>
       </c>
       <c r="R93" t="n">
-        <v>6828079</v>
+        <v>6828201</v>
       </c>
       <c r="S93" t="n">
         <v>14</v>
@@ -10958,7 +10959,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10968,7 +10969,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10994,13 +10995,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768982</t>
+          <t>https://artportalen.se/Sighting/135768977</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135768988</v>
+        <v>135768982</v>
       </c>
       <c r="B94" t="n">
         <v>80031</v>
@@ -11035,13 +11036,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476704</v>
+        <v>476637</v>
       </c>
       <c r="R94" t="n">
-        <v>6827963</v>
+        <v>6828079</v>
       </c>
       <c r="S94" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11070,7 +11071,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11080,7 +11081,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11106,13 +11107,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768988</t>
+          <t>https://artportalen.se/Sighting/135768982</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135768994</v>
+        <v>135768988</v>
       </c>
       <c r="B95" t="n">
         <v>80031</v>
@@ -11147,13 +11148,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>476845</v>
+        <v>476704</v>
       </c>
       <c r="R95" t="n">
-        <v>6827898</v>
+        <v>6827963</v>
       </c>
       <c r="S95" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11182,7 +11183,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11192,7 +11193,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11218,13 +11219,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768994</t>
+          <t>https://artportalen.se/Sighting/135768988</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135768996</v>
+        <v>135768994</v>
       </c>
       <c r="B96" t="n">
         <v>80031</v>
@@ -11259,13 +11260,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476895</v>
+        <v>476845</v>
       </c>
       <c r="R96" t="n">
-        <v>6827863</v>
+        <v>6827898</v>
       </c>
       <c r="S96" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11294,7 +11295,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11304,7 +11305,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11330,13 +11331,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768996</t>
+          <t>https://artportalen.se/Sighting/135768994</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135769018</v>
+        <v>135768996</v>
       </c>
       <c r="B97" t="n">
         <v>80031</v>
@@ -11371,13 +11372,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476860</v>
+        <v>476895</v>
       </c>
       <c r="R97" t="n">
-        <v>6828159</v>
+        <v>6827863</v>
       </c>
       <c r="S97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11406,7 +11407,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11416,7 +11417,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11442,13 +11443,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769018</t>
+          <t>https://artportalen.se/Sighting/135768996</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135769034</v>
+        <v>135769018</v>
       </c>
       <c r="B98" t="n">
         <v>80031</v>
@@ -11483,13 +11484,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476909</v>
+        <v>476860</v>
       </c>
       <c r="R98" t="n">
-        <v>6828446</v>
+        <v>6828159</v>
       </c>
       <c r="S98" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11518,7 +11519,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11528,7 +11529,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11554,13 +11555,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769034</t>
+          <t>https://artportalen.se/Sighting/135769018</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135769074</v>
+        <v>135769034</v>
       </c>
       <c r="B99" t="n">
         <v>80031</v>
@@ -11595,13 +11596,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476691</v>
+        <v>476909</v>
       </c>
       <c r="R99" t="n">
-        <v>6828492</v>
+        <v>6828446</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11630,7 +11631,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11640,7 +11641,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11665,6 +11666,118 @@
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769034</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>135769074</v>
+      </c>
+      <c r="B100" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lilla atjomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>476691</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6828492</v>
+      </c>
+      <c r="S100" t="n">
+        <v>15</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135769074</t>
         </is>
@@ -11770,6 +11883,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ100"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8074,10 +8074,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135769032</v>
+        <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>78445</v>
+        <v>80556</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8085,37 +8085,44 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6487</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lilla atjomäck, Dlr</t>
+          <t>Lilla Ajtomäck, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>476906</v>
+        <v>476803</v>
       </c>
       <c r="R68" t="n">
-        <v>6828445</v>
+        <v>6828731</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8139,22 +8146,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under naturvärdesbedömning av Orsa Besparingsskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8163,30 +8165,31 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769032</t>
+          <t>https://artportalen.se/Sighting/135534875</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135769039</v>
+        <v>135769032</v>
       </c>
       <c r="B69" t="n">
         <v>78445</v>
@@ -8221,13 +8224,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476914</v>
+        <v>476906</v>
       </c>
       <c r="R69" t="n">
-        <v>6828350</v>
+        <v>6828445</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8256,7 +8259,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8266,7 +8269,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8292,16 +8295,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769039</t>
+          <t>https://artportalen.se/Sighting/135769032</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135769010</v>
+        <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>57980</v>
+        <v>78445</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8309,39 +8312,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lilla atjomäck, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>476720</v>
+        <v>476914</v>
       </c>
       <c r="R70" t="n">
-        <v>6828070</v>
+        <v>6828350</v>
       </c>
       <c r="S70" t="n">
         <v>9</v>
@@ -8373,7 +8371,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8383,7 +8381,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8409,44 +8407,44 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769010</t>
+          <t>https://artportalen.se/Sighting/135769039</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135769011</v>
+        <v>135769010</v>
       </c>
       <c r="B71" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8455,13 +8453,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476722</v>
+        <v>476720</v>
       </c>
       <c r="R71" t="n">
-        <v>6828166</v>
+        <v>6828070</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8490,7 +8488,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8500,7 +8498,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8526,59 +8524,70 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769011</t>
+          <t>https://artportalen.se/Sighting/135769010</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135769052</v>
+        <v>135534822</v>
       </c>
       <c r="B72" t="n">
-        <v>5180</v>
+        <v>57167</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lilla atjomäck, Dlr</t>
+          <t>Lilla Ajtomäck, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>477011</v>
+        <v>476923</v>
       </c>
       <c r="R72" t="n">
-        <v>6828245</v>
+        <v>6828512</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8602,22 +8611,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Påträffad under naturvärdesbedömning av Orsa Besparingsskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8632,65 +8636,70 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769052</t>
+          <t>https://artportalen.se/Sighting/135534822</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135769078</v>
+        <v>135769011</v>
       </c>
       <c r="B73" t="n">
-        <v>58141</v>
+        <v>57167</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lilla atjomäck, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476724</v>
+        <v>476722</v>
       </c>
       <c r="R73" t="n">
-        <v>6828863</v>
+        <v>6828166</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8719,7 +8728,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8729,7 +8738,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8755,54 +8764,59 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769078</t>
+          <t>https://artportalen.se/Sighting/135769011</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135769004</v>
+        <v>135769052</v>
       </c>
       <c r="B74" t="n">
-        <v>98144</v>
+        <v>5180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>102204</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lilla atjomäck, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476877</v>
+        <v>477011</v>
       </c>
       <c r="R74" t="n">
-        <v>6827984</v>
+        <v>6828245</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8831,7 +8845,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8841,7 +8855,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8867,38 +8881,38 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769004</t>
+          <t>https://artportalen.se/Sighting/135769052</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135769042</v>
+        <v>135769078</v>
       </c>
       <c r="B75" t="n">
-        <v>98144</v>
+        <v>58141</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8908,13 +8922,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>477009</v>
+        <v>476724</v>
       </c>
       <c r="R75" t="n">
-        <v>6828275</v>
+        <v>6828863</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8943,7 +8957,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8953,7 +8967,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8979,16 +8993,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769042</t>
+          <t>https://artportalen.se/Sighting/135769078</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135768992</v>
+        <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98138</v>
+        <v>98144</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8996,16 +9010,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9020,10 +9034,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476723</v>
+        <v>476877</v>
       </c>
       <c r="R76" t="n">
-        <v>6827952</v>
+        <v>6827984</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9055,7 +9069,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9065,7 +9079,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9091,38 +9105,38 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768992</t>
+          <t>https://artportalen.se/Sighting/135769004</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135768980</v>
+        <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>79199</v>
+        <v>98144</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9132,13 +9146,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476631</v>
+        <v>477009</v>
       </c>
       <c r="R77" t="n">
-        <v>6828169</v>
+        <v>6828275</v>
       </c>
       <c r="S77" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9167,7 +9181,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9177,7 +9191,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9203,38 +9217,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768980</t>
+          <t>https://artportalen.se/Sighting/135769042</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135768983</v>
+        <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>79199</v>
+        <v>98138</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9244,13 +9258,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476635</v>
+        <v>476723</v>
       </c>
       <c r="R78" t="n">
-        <v>6828068</v>
+        <v>6827952</v>
       </c>
       <c r="S78" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9279,7 +9293,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9289,7 +9303,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9315,13 +9329,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768983</t>
+          <t>https://artportalen.se/Sighting/135768992</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135768985</v>
+        <v>135768980</v>
       </c>
       <c r="B79" t="n">
         <v>79199</v>
@@ -9356,13 +9370,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476662</v>
+        <v>476631</v>
       </c>
       <c r="R79" t="n">
-        <v>6827985</v>
+        <v>6828169</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9391,7 +9405,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9401,7 +9415,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9427,13 +9441,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768985</t>
+          <t>https://artportalen.se/Sighting/135768980</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135768989</v>
+        <v>135768983</v>
       </c>
       <c r="B80" t="n">
         <v>79199</v>
@@ -9468,13 +9482,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476706</v>
+        <v>476635</v>
       </c>
       <c r="R80" t="n">
-        <v>6827964</v>
+        <v>6828068</v>
       </c>
       <c r="S80" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9503,7 +9517,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9513,7 +9527,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9539,13 +9553,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768989</t>
+          <t>https://artportalen.se/Sighting/135768983</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135768995</v>
+        <v>135768985</v>
       </c>
       <c r="B81" t="n">
         <v>79199</v>
@@ -9580,13 +9594,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476840</v>
+        <v>476662</v>
       </c>
       <c r="R81" t="n">
-        <v>6827894</v>
+        <v>6827985</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9615,7 +9629,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9625,7 +9639,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9651,13 +9665,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768995</t>
+          <t>https://artportalen.se/Sighting/135768985</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135768999</v>
+        <v>135768989</v>
       </c>
       <c r="B82" t="n">
         <v>79199</v>
@@ -9692,13 +9706,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476881</v>
+        <v>476706</v>
       </c>
       <c r="R82" t="n">
-        <v>6827947</v>
+        <v>6827964</v>
       </c>
       <c r="S82" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9727,7 +9741,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9737,7 +9751,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9763,13 +9777,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768999</t>
+          <t>https://artportalen.se/Sighting/135768989</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135769008</v>
+        <v>135768995</v>
       </c>
       <c r="B83" t="n">
         <v>79199</v>
@@ -9804,13 +9818,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476776</v>
+        <v>476840</v>
       </c>
       <c r="R83" t="n">
-        <v>6828033</v>
+        <v>6827894</v>
       </c>
       <c r="S83" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9839,7 +9853,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9849,7 +9863,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9875,13 +9889,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769008</t>
+          <t>https://artportalen.se/Sighting/135768995</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135769019</v>
+        <v>135768999</v>
       </c>
       <c r="B84" t="n">
         <v>79199</v>
@@ -9916,13 +9930,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476864</v>
+        <v>476881</v>
       </c>
       <c r="R84" t="n">
-        <v>6828186</v>
+        <v>6827947</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9951,7 +9965,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9961,7 +9975,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9987,13 +10001,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769019</t>
+          <t>https://artportalen.se/Sighting/135768999</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135769025</v>
+        <v>135769008</v>
       </c>
       <c r="B85" t="n">
         <v>79199</v>
@@ -10028,13 +10042,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476708</v>
+        <v>476776</v>
       </c>
       <c r="R85" t="n">
-        <v>6828618</v>
+        <v>6828033</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10063,7 +10077,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10073,7 +10087,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10099,13 +10113,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769025</t>
+          <t>https://artportalen.se/Sighting/135769008</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135769028</v>
+        <v>135769019</v>
       </c>
       <c r="B86" t="n">
         <v>79199</v>
@@ -10140,13 +10154,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476743</v>
+        <v>476864</v>
       </c>
       <c r="R86" t="n">
-        <v>6828616</v>
+        <v>6828186</v>
       </c>
       <c r="S86" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10175,7 +10189,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10185,7 +10199,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10211,13 +10225,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769028</t>
+          <t>https://artportalen.se/Sighting/135769019</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135769046</v>
+        <v>135769025</v>
       </c>
       <c r="B87" t="n">
         <v>79199</v>
@@ -10252,13 +10266,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>477084</v>
+        <v>476708</v>
       </c>
       <c r="R87" t="n">
-        <v>6828344</v>
+        <v>6828618</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10287,7 +10301,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10297,7 +10311,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10323,13 +10337,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769046</t>
+          <t>https://artportalen.se/Sighting/135769025</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135769048</v>
+        <v>135769028</v>
       </c>
       <c r="B88" t="n">
         <v>79199</v>
@@ -10364,13 +10378,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>477083</v>
+        <v>476743</v>
       </c>
       <c r="R88" t="n">
-        <v>6828378</v>
+        <v>6828616</v>
       </c>
       <c r="S88" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10399,7 +10413,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10409,7 +10423,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10435,13 +10449,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769048</t>
+          <t>https://artportalen.se/Sighting/135769028</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135769059</v>
+        <v>135769046</v>
       </c>
       <c r="B89" t="n">
         <v>79199</v>
@@ -10476,13 +10490,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476732</v>
+        <v>477084</v>
       </c>
       <c r="R89" t="n">
-        <v>6828298</v>
+        <v>6828344</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10511,7 +10525,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10521,7 +10535,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10547,13 +10561,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769059</t>
+          <t>https://artportalen.se/Sighting/135769046</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135769063</v>
+        <v>135769048</v>
       </c>
       <c r="B90" t="n">
         <v>79199</v>
@@ -10588,13 +10602,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476661</v>
+        <v>477083</v>
       </c>
       <c r="R90" t="n">
-        <v>6828289</v>
+        <v>6828378</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10623,7 +10637,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10633,7 +10647,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10659,13 +10673,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769063</t>
+          <t>https://artportalen.se/Sighting/135769048</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135769064</v>
+        <v>135769059</v>
       </c>
       <c r="B91" t="n">
         <v>79199</v>
@@ -10700,13 +10714,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476627</v>
+        <v>476732</v>
       </c>
       <c r="R91" t="n">
-        <v>6828296</v>
+        <v>6828298</v>
       </c>
       <c r="S91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10735,7 +10749,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10745,7 +10759,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10771,13 +10785,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769064</t>
+          <t>https://artportalen.se/Sighting/135769059</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135769070</v>
+        <v>135769063</v>
       </c>
       <c r="B92" t="n">
         <v>79199</v>
@@ -10812,13 +10826,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476703</v>
+        <v>476661</v>
       </c>
       <c r="R92" t="n">
-        <v>6828355</v>
+        <v>6828289</v>
       </c>
       <c r="S92" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10847,7 +10861,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10857,7 +10871,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10883,16 +10897,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769070</t>
+          <t>https://artportalen.se/Sighting/135769063</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135768977</v>
+        <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>80031</v>
+        <v>79199</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10900,21 +10914,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10924,13 +10938,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476559</v>
+        <v>476627</v>
       </c>
       <c r="R93" t="n">
-        <v>6828201</v>
+        <v>6828296</v>
       </c>
       <c r="S93" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10959,7 +10973,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10969,7 +10983,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10995,16 +11009,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768977</t>
+          <t>https://artportalen.se/Sighting/135769064</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135768982</v>
+        <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>80031</v>
+        <v>79199</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11012,21 +11026,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11036,13 +11050,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476637</v>
+        <v>476703</v>
       </c>
       <c r="R94" t="n">
-        <v>6828079</v>
+        <v>6828355</v>
       </c>
       <c r="S94" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11071,7 +11085,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11081,7 +11095,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11107,13 +11121,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768982</t>
+          <t>https://artportalen.se/Sighting/135769070</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135768988</v>
+        <v>135768977</v>
       </c>
       <c r="B95" t="n">
         <v>80031</v>
@@ -11148,13 +11162,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>476704</v>
+        <v>476559</v>
       </c>
       <c r="R95" t="n">
-        <v>6827963</v>
+        <v>6828201</v>
       </c>
       <c r="S95" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11183,7 +11197,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11193,7 +11207,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11219,13 +11233,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768988</t>
+          <t>https://artportalen.se/Sighting/135768977</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135768994</v>
+        <v>135768982</v>
       </c>
       <c r="B96" t="n">
         <v>80031</v>
@@ -11260,13 +11274,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476845</v>
+        <v>476637</v>
       </c>
       <c r="R96" t="n">
-        <v>6827898</v>
+        <v>6828079</v>
       </c>
       <c r="S96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11295,7 +11309,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11305,7 +11319,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11331,13 +11345,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768994</t>
+          <t>https://artportalen.se/Sighting/135768982</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135768996</v>
+        <v>135768988</v>
       </c>
       <c r="B97" t="n">
         <v>80031</v>
@@ -11372,13 +11386,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476895</v>
+        <v>476704</v>
       </c>
       <c r="R97" t="n">
-        <v>6827863</v>
+        <v>6827963</v>
       </c>
       <c r="S97" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11407,7 +11421,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11417,7 +11431,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11443,13 +11457,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135768996</t>
+          <t>https://artportalen.se/Sighting/135768988</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135769018</v>
+        <v>135768994</v>
       </c>
       <c r="B98" t="n">
         <v>80031</v>
@@ -11484,13 +11498,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476860</v>
+        <v>476845</v>
       </c>
       <c r="R98" t="n">
-        <v>6828159</v>
+        <v>6827898</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11519,7 +11533,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11529,7 +11543,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11555,13 +11569,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769018</t>
+          <t>https://artportalen.se/Sighting/135768994</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135769034</v>
+        <v>135768996</v>
       </c>
       <c r="B99" t="n">
         <v>80031</v>
@@ -11596,13 +11610,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476909</v>
+        <v>476895</v>
       </c>
       <c r="R99" t="n">
-        <v>6828446</v>
+        <v>6827863</v>
       </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11631,7 +11645,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11641,7 +11655,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11667,13 +11681,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135769034</t>
+          <t>https://artportalen.se/Sighting/135768996</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135769074</v>
+        <v>135769018</v>
       </c>
       <c r="B100" t="n">
         <v>80031</v>
@@ -11708,13 +11722,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476691</v>
+        <v>476860</v>
       </c>
       <c r="R100" t="n">
-        <v>6828492</v>
+        <v>6828159</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11743,7 +11757,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11753,7 +11767,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11778,6 +11792,230 @@
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769018</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>135769034</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lilla atjomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>476909</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6828446</v>
+      </c>
+      <c r="S101" t="n">
+        <v>8</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135769034</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>135769074</v>
+      </c>
+      <c r="B102" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Lilla atjomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>476691</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6828492</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135769074</t>
         </is>
@@ -11884,6 +12122,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135768993</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135768997</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135769026</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135769050</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135769057</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135769017</v>
       </c>
       <c r="B9" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135769031</v>
       </c>
       <c r="B10" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93341</v>
+        <v>93356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>135768973</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135768979</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135769003</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>135769023</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>135769036</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135769043</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135769045</v>
       </c>
       <c r="B42" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135769051</v>
       </c>
       <c r="B43" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>135769006</v>
       </c>
       <c r="B45" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135768991</v>
       </c>
       <c r="B47" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135769000</v>
       </c>
       <c r="B48" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135769005</v>
       </c>
       <c r="B49" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135769016</v>
       </c>
       <c r="B50" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>135769029</v>
       </c>
       <c r="B51" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>135769030</v>
       </c>
       <c r="B52" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135769033</v>
       </c>
       <c r="B53" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135769035</v>
       </c>
       <c r="B54" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135768990</v>
       </c>
       <c r="B56" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>135769002</v>
       </c>
       <c r="B58" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135769007</v>
       </c>
       <c r="B59" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>135769021</v>
       </c>
       <c r="B60" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135769022</v>
       </c>
       <c r="B61" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135769027</v>
       </c>
       <c r="B62" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>135769037</v>
       </c>
       <c r="B63" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135769047</v>
       </c>
       <c r="B64" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135769058</v>
       </c>
       <c r="B65" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>135769071</v>
       </c>
       <c r="B66" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>135769032</v>
       </c>
       <c r="B69" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>135769010</v>
       </c>
       <c r="B71" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>135534822</v>
       </c>
       <c r="B72" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>135769011</v>
       </c>
       <c r="B73" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>135769052</v>
       </c>
       <c r="B74" t="n">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>135769078</v>
       </c>
       <c r="B75" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>135768980</v>
       </c>
       <c r="B79" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135768983</v>
       </c>
       <c r="B80" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135768985</v>
       </c>
       <c r="B81" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>135768989</v>
       </c>
       <c r="B82" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>135768995</v>
       </c>
       <c r="B83" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>135768999</v>
       </c>
       <c r="B84" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>135769008</v>
       </c>
       <c r="B85" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>135769019</v>
       </c>
       <c r="B86" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769025</v>
       </c>
       <c r="B87" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>135769028</v>
       </c>
       <c r="B88" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>135769046</v>
       </c>
       <c r="B89" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>135769048</v>
       </c>
       <c r="B90" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>135769059</v>
       </c>
       <c r="B91" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>135769063</v>
       </c>
       <c r="B92" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>135768977</v>
       </c>
       <c r="B95" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>135768982</v>
       </c>
       <c r="B96" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>135768988</v>
       </c>
       <c r="B97" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>135768994</v>
       </c>
       <c r="B98" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135768996</v>
       </c>
       <c r="B99" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135769018</v>
       </c>
       <c r="B100" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>135769034</v>
       </c>
       <c r="B101" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135769074</v>
       </c>
       <c r="B102" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135768993</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135768997</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135769026</v>
       </c>
       <c r="B5" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135769050</v>
       </c>
       <c r="B6" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135769057</v>
       </c>
       <c r="B7" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135769017</v>
       </c>
       <c r="B9" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135769031</v>
       </c>
       <c r="B10" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>135768973</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135768979</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135769003</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>135769023</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>135769036</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135769043</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135769045</v>
       </c>
       <c r="B42" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135769051</v>
       </c>
       <c r="B43" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>135769006</v>
       </c>
       <c r="B45" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135768991</v>
       </c>
       <c r="B47" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135769000</v>
       </c>
       <c r="B48" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135769005</v>
       </c>
       <c r="B49" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135769016</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>135769029</v>
       </c>
       <c r="B51" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>135769030</v>
       </c>
       <c r="B52" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135769033</v>
       </c>
       <c r="B53" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135769035</v>
       </c>
       <c r="B54" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135768990</v>
       </c>
       <c r="B56" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>135769002</v>
       </c>
       <c r="B58" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135769007</v>
       </c>
       <c r="B59" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>135769021</v>
       </c>
       <c r="B60" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135769022</v>
       </c>
       <c r="B61" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135769027</v>
       </c>
       <c r="B62" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>135769037</v>
       </c>
       <c r="B63" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135769047</v>
       </c>
       <c r="B64" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135769058</v>
       </c>
       <c r="B65" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>135769071</v>
       </c>
       <c r="B66" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>135769032</v>
       </c>
       <c r="B69" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>135768980</v>
       </c>
       <c r="B79" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135768983</v>
       </c>
       <c r="B80" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135768985</v>
       </c>
       <c r="B81" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>135768989</v>
       </c>
       <c r="B82" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>135768995</v>
       </c>
       <c r="B83" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>135768999</v>
       </c>
       <c r="B84" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>135769008</v>
       </c>
       <c r="B85" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>135769019</v>
       </c>
       <c r="B86" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769025</v>
       </c>
       <c r="B87" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>135769028</v>
       </c>
       <c r="B88" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>135769046</v>
       </c>
       <c r="B89" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>135769048</v>
       </c>
       <c r="B90" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>135769059</v>
       </c>
       <c r="B91" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>135769063</v>
       </c>
       <c r="B92" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>135768977</v>
       </c>
       <c r="B95" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>135768982</v>
       </c>
       <c r="B96" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>135768988</v>
       </c>
       <c r="B97" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>135768994</v>
       </c>
       <c r="B98" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135768996</v>
       </c>
       <c r="B99" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135769018</v>
       </c>
       <c r="B100" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>135769034</v>
       </c>
       <c r="B101" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135769074</v>
       </c>
       <c r="B102" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93357</v>
+        <v>93358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135768993</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135768997</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135769026</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135769050</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135769057</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135769017</v>
       </c>
       <c r="B9" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135769031</v>
       </c>
       <c r="B10" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>135768973</v>
       </c>
       <c r="B36" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135768979</v>
       </c>
       <c r="B37" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135769003</v>
       </c>
       <c r="B38" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>135769023</v>
       </c>
       <c r="B39" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>135769036</v>
       </c>
       <c r="B40" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135769043</v>
       </c>
       <c r="B41" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135769045</v>
       </c>
       <c r="B42" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135769051</v>
       </c>
       <c r="B43" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>135769006</v>
       </c>
       <c r="B45" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135768991</v>
       </c>
       <c r="B47" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135769000</v>
       </c>
       <c r="B48" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135769005</v>
       </c>
       <c r="B49" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135769016</v>
       </c>
       <c r="B50" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>135769029</v>
       </c>
       <c r="B51" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>135769030</v>
       </c>
       <c r="B52" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135769033</v>
       </c>
       <c r="B53" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135769035</v>
       </c>
       <c r="B54" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135768990</v>
       </c>
       <c r="B56" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>135769002</v>
       </c>
       <c r="B58" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135769007</v>
       </c>
       <c r="B59" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>135769021</v>
       </c>
       <c r="B60" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135769022</v>
       </c>
       <c r="B61" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135769027</v>
       </c>
       <c r="B62" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>135769037</v>
       </c>
       <c r="B63" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135769047</v>
       </c>
       <c r="B64" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135769058</v>
       </c>
       <c r="B65" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>135769071</v>
       </c>
       <c r="B66" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>135769032</v>
       </c>
       <c r="B69" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>135769010</v>
       </c>
       <c r="B71" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>135534822</v>
       </c>
       <c r="B72" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>135769011</v>
       </c>
       <c r="B73" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>135769078</v>
       </c>
       <c r="B75" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>135768980</v>
       </c>
       <c r="B79" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135768983</v>
       </c>
       <c r="B80" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135768985</v>
       </c>
       <c r="B81" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>135768989</v>
       </c>
       <c r="B82" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>135768995</v>
       </c>
       <c r="B83" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>135768999</v>
       </c>
       <c r="B84" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>135769008</v>
       </c>
       <c r="B85" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>135769019</v>
       </c>
       <c r="B86" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769025</v>
       </c>
       <c r="B87" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>135769028</v>
       </c>
       <c r="B88" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>135769046</v>
       </c>
       <c r="B89" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>135769048</v>
       </c>
       <c r="B90" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>135769059</v>
       </c>
       <c r="B91" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>135769063</v>
       </c>
       <c r="B92" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>135768977</v>
       </c>
       <c r="B95" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>135768982</v>
       </c>
       <c r="B96" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>135768988</v>
       </c>
       <c r="B97" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>135768994</v>
       </c>
       <c r="B98" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135768996</v>
       </c>
       <c r="B99" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135769018</v>
       </c>
       <c r="B100" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>135769034</v>
       </c>
       <c r="B101" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135769074</v>
       </c>
       <c r="B102" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135768993</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135768997</v>
       </c>
       <c r="B4" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135769026</v>
       </c>
       <c r="B5" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135769050</v>
       </c>
       <c r="B6" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135769057</v>
       </c>
       <c r="B7" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135769017</v>
       </c>
       <c r="B9" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135769031</v>
       </c>
       <c r="B10" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93359</v>
+        <v>93365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>135768973</v>
       </c>
       <c r="B36" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135768979</v>
       </c>
       <c r="B37" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135769003</v>
       </c>
       <c r="B38" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>135769023</v>
       </c>
       <c r="B39" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>135769036</v>
       </c>
       <c r="B40" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135769043</v>
       </c>
       <c r="B41" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135769045</v>
       </c>
       <c r="B42" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135769051</v>
       </c>
       <c r="B43" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>135769006</v>
       </c>
       <c r="B45" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135768991</v>
       </c>
       <c r="B47" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135769000</v>
       </c>
       <c r="B48" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135769005</v>
       </c>
       <c r="B49" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135769016</v>
       </c>
       <c r="B50" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>135769029</v>
       </c>
       <c r="B51" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>135769030</v>
       </c>
       <c r="B52" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135769033</v>
       </c>
       <c r="B53" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135769035</v>
       </c>
       <c r="B54" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135768990</v>
       </c>
       <c r="B56" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>135769002</v>
       </c>
       <c r="B58" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135769007</v>
       </c>
       <c r="B59" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>135769021</v>
       </c>
       <c r="B60" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135769022</v>
       </c>
       <c r="B61" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135769027</v>
       </c>
       <c r="B62" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>135769037</v>
       </c>
       <c r="B63" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135769047</v>
       </c>
       <c r="B64" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135769058</v>
       </c>
       <c r="B65" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>135769071</v>
       </c>
       <c r="B66" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>135769032</v>
       </c>
       <c r="B69" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>135769010</v>
       </c>
       <c r="B71" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>135534822</v>
       </c>
       <c r="B72" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>135769011</v>
       </c>
       <c r="B73" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>135769078</v>
       </c>
       <c r="B75" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>135768980</v>
       </c>
       <c r="B79" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135768983</v>
       </c>
       <c r="B80" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135768985</v>
       </c>
       <c r="B81" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>135768989</v>
       </c>
       <c r="B82" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>135768995</v>
       </c>
       <c r="B83" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>135768999</v>
       </c>
       <c r="B84" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>135769008</v>
       </c>
       <c r="B85" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>135769019</v>
       </c>
       <c r="B86" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769025</v>
       </c>
       <c r="B87" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>135769028</v>
       </c>
       <c r="B88" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>135769046</v>
       </c>
       <c r="B89" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>135769048</v>
       </c>
       <c r="B90" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>135769059</v>
       </c>
       <c r="B91" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>135769063</v>
       </c>
       <c r="B92" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>135768977</v>
       </c>
       <c r="B95" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>135768982</v>
       </c>
       <c r="B96" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>135768988</v>
       </c>
       <c r="B97" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>135768994</v>
       </c>
       <c r="B98" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135768996</v>
       </c>
       <c r="B99" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135769018</v>
       </c>
       <c r="B100" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>135769034</v>
       </c>
       <c r="B101" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135769074</v>
       </c>
       <c r="B102" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135768993</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135768997</v>
       </c>
       <c r="B4" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135769026</v>
       </c>
       <c r="B5" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135769050</v>
       </c>
       <c r="B6" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135769057</v>
       </c>
       <c r="B7" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135769017</v>
       </c>
       <c r="B9" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135769031</v>
       </c>
       <c r="B10" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93365</v>
+        <v>93366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>135768973</v>
       </c>
       <c r="B36" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135768979</v>
       </c>
       <c r="B37" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135769003</v>
       </c>
       <c r="B38" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>135769023</v>
       </c>
       <c r="B39" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>135769036</v>
       </c>
       <c r="B40" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135769043</v>
       </c>
       <c r="B41" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135769045</v>
       </c>
       <c r="B42" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135769051</v>
       </c>
       <c r="B43" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>135769006</v>
       </c>
       <c r="B45" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135768991</v>
       </c>
       <c r="B47" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135769000</v>
       </c>
       <c r="B48" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135769005</v>
       </c>
       <c r="B49" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135769016</v>
       </c>
       <c r="B50" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>135769029</v>
       </c>
       <c r="B51" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>135769030</v>
       </c>
       <c r="B52" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135769033</v>
       </c>
       <c r="B53" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135769035</v>
       </c>
       <c r="B54" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135768990</v>
       </c>
       <c r="B56" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>135769002</v>
       </c>
       <c r="B58" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135769007</v>
       </c>
       <c r="B59" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>135769021</v>
       </c>
       <c r="B60" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135769022</v>
       </c>
       <c r="B61" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135769027</v>
       </c>
       <c r="B62" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>135769037</v>
       </c>
       <c r="B63" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135769047</v>
       </c>
       <c r="B64" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135769058</v>
       </c>
       <c r="B65" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>135769071</v>
       </c>
       <c r="B66" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>135769032</v>
       </c>
       <c r="B69" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>135769010</v>
       </c>
       <c r="B71" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>135534822</v>
       </c>
       <c r="B72" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>135769011</v>
       </c>
       <c r="B73" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>135769078</v>
       </c>
       <c r="B75" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>135768980</v>
       </c>
       <c r="B79" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135768983</v>
       </c>
       <c r="B80" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135768985</v>
       </c>
       <c r="B81" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>135768989</v>
       </c>
       <c r="B82" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>135768995</v>
       </c>
       <c r="B83" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>135768999</v>
       </c>
       <c r="B84" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>135769008</v>
       </c>
       <c r="B85" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>135769019</v>
       </c>
       <c r="B86" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769025</v>
       </c>
       <c r="B87" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>135769028</v>
       </c>
       <c r="B88" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>135769046</v>
       </c>
       <c r="B89" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>135769048</v>
       </c>
       <c r="B90" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>135769059</v>
       </c>
       <c r="B91" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>135769063</v>
       </c>
       <c r="B92" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>135768977</v>
       </c>
       <c r="B95" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>135768982</v>
       </c>
       <c r="B96" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>135768988</v>
       </c>
       <c r="B97" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>135768994</v>
       </c>
       <c r="B98" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135768996</v>
       </c>
       <c r="B99" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135769018</v>
       </c>
       <c r="B100" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>135769034</v>
       </c>
       <c r="B101" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135769074</v>
       </c>
       <c r="B102" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135768993</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135768997</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135769026</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135769050</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135769057</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135769017</v>
       </c>
       <c r="B9" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135769031</v>
       </c>
       <c r="B10" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93366</v>
+        <v>93372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>135768973</v>
       </c>
       <c r="B36" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135768979</v>
       </c>
       <c r="B37" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135769003</v>
       </c>
       <c r="B38" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>135769023</v>
       </c>
       <c r="B39" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>135769036</v>
       </c>
       <c r="B40" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135769043</v>
       </c>
       <c r="B41" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135769045</v>
       </c>
       <c r="B42" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135769051</v>
       </c>
       <c r="B43" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>135769006</v>
       </c>
       <c r="B45" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>79474</v>
+        <v>79478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135768991</v>
       </c>
       <c r="B47" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135769000</v>
       </c>
       <c r="B48" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135769005</v>
       </c>
       <c r="B49" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135769016</v>
       </c>
       <c r="B50" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>135769029</v>
       </c>
       <c r="B51" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>135769030</v>
       </c>
       <c r="B52" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135769033</v>
       </c>
       <c r="B53" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135769035</v>
       </c>
       <c r="B54" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135768990</v>
       </c>
       <c r="B56" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>135769002</v>
       </c>
       <c r="B58" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135769007</v>
       </c>
       <c r="B59" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>135769021</v>
       </c>
       <c r="B60" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135769022</v>
       </c>
       <c r="B61" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135769027</v>
       </c>
       <c r="B62" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>135769037</v>
       </c>
       <c r="B63" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135769047</v>
       </c>
       <c r="B64" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135769058</v>
       </c>
       <c r="B65" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>135769071</v>
       </c>
       <c r="B66" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>135769032</v>
       </c>
       <c r="B69" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>135768980</v>
       </c>
       <c r="B79" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135768983</v>
       </c>
       <c r="B80" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135768985</v>
       </c>
       <c r="B81" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>135768989</v>
       </c>
       <c r="B82" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>135768995</v>
       </c>
       <c r="B83" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>135768999</v>
       </c>
       <c r="B84" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>135769008</v>
       </c>
       <c r="B85" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>135769019</v>
       </c>
       <c r="B86" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769025</v>
       </c>
       <c r="B87" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>135769028</v>
       </c>
       <c r="B88" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>135769046</v>
       </c>
       <c r="B89" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>135769048</v>
       </c>
       <c r="B90" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>135769059</v>
       </c>
       <c r="B91" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>135769063</v>
       </c>
       <c r="B92" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>135768977</v>
       </c>
       <c r="B95" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>135768982</v>
       </c>
       <c r="B96" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>135768988</v>
       </c>
       <c r="B97" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>135768994</v>
       </c>
       <c r="B98" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135768996</v>
       </c>
       <c r="B99" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135769018</v>
       </c>
       <c r="B100" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>135769034</v>
       </c>
       <c r="B101" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135769074</v>
       </c>
       <c r="B102" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135768993</v>
       </c>
       <c r="B3" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>135768997</v>
       </c>
       <c r="B4" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>135769026</v>
       </c>
       <c r="B5" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>135769050</v>
       </c>
       <c r="B6" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>135769057</v>
       </c>
       <c r="B7" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>135769060</v>
       </c>
       <c r="B8" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135769017</v>
       </c>
       <c r="B9" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135769031</v>
       </c>
       <c r="B10" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135769041</v>
       </c>
       <c r="B11" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135769040</v>
       </c>
       <c r="B12" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135768978</v>
       </c>
       <c r="B13" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>135769001</v>
       </c>
       <c r="B14" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>135769055</v>
       </c>
       <c r="B15" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>135769080</v>
       </c>
       <c r="B16" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>135769081</v>
       </c>
       <c r="B17" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>135768987</v>
       </c>
       <c r="B18" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>135769056</v>
       </c>
       <c r="B19" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>135769067</v>
       </c>
       <c r="B20" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>135769077</v>
       </c>
       <c r="B21" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>135769083</v>
       </c>
       <c r="B22" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>135769085</v>
       </c>
       <c r="B23" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>135768986</v>
       </c>
       <c r="B24" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>135768998</v>
       </c>
       <c r="B25" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>135768974</v>
       </c>
       <c r="B26" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>135768975</v>
       </c>
       <c r="B27" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>135768984</v>
       </c>
       <c r="B28" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>135769009</v>
       </c>
       <c r="B29" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>135769013</v>
       </c>
       <c r="B30" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>135769014</v>
       </c>
       <c r="B31" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>135769024</v>
       </c>
       <c r="B32" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>135769061</v>
       </c>
       <c r="B33" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135769062</v>
       </c>
       <c r="B34" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         <v>135769068</v>
       </c>
       <c r="B35" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>135768973</v>
       </c>
       <c r="B36" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>135768979</v>
       </c>
       <c r="B37" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135769003</v>
       </c>
       <c r="B38" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>135769023</v>
       </c>
       <c r="B39" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>135769036</v>
       </c>
       <c r="B40" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135769043</v>
       </c>
       <c r="B41" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>135769045</v>
       </c>
       <c r="B42" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>135769051</v>
       </c>
       <c r="B43" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>135769053</v>
       </c>
       <c r="B44" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>135769006</v>
       </c>
       <c r="B45" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>135769073</v>
       </c>
       <c r="B46" t="n">
-        <v>79478</v>
+        <v>79484</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>135768991</v>
       </c>
       <c r="B47" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>135769000</v>
       </c>
       <c r="B48" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135769005</v>
       </c>
       <c r="B49" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>135769016</v>
       </c>
       <c r="B50" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>135769029</v>
       </c>
       <c r="B51" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>135769030</v>
       </c>
       <c r="B52" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>135769033</v>
       </c>
       <c r="B53" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>135769035</v>
       </c>
       <c r="B54" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>135769066</v>
       </c>
       <c r="B55" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>135768990</v>
       </c>
       <c r="B56" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>135769015</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>135769002</v>
       </c>
       <c r="B58" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>135769007</v>
       </c>
       <c r="B59" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>135769021</v>
       </c>
       <c r="B60" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>135769022</v>
       </c>
       <c r="B61" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>135769027</v>
       </c>
       <c r="B62" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>135769037</v>
       </c>
       <c r="B63" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>135769047</v>
       </c>
       <c r="B64" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>135769058</v>
       </c>
       <c r="B65" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>135769071</v>
       </c>
       <c r="B66" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>135769076</v>
       </c>
       <c r="B67" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>135769032</v>
       </c>
       <c r="B69" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135769039</v>
       </c>
       <c r="B70" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>135769010</v>
       </c>
       <c r="B71" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>135534822</v>
       </c>
       <c r="B72" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>135769011</v>
       </c>
       <c r="B73" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>135769078</v>
       </c>
       <c r="B75" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>135769004</v>
       </c>
       <c r="B76" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>135769042</v>
       </c>
       <c r="B77" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>135768992</v>
       </c>
       <c r="B78" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>135768980</v>
       </c>
       <c r="B79" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>135768983</v>
       </c>
       <c r="B80" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135768985</v>
       </c>
       <c r="B81" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>135768989</v>
       </c>
       <c r="B82" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>135768995</v>
       </c>
       <c r="B83" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>135768999</v>
       </c>
       <c r="B84" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>135769008</v>
       </c>
       <c r="B85" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>135769019</v>
       </c>
       <c r="B86" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>135769025</v>
       </c>
       <c r="B87" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>135769028</v>
       </c>
       <c r="B88" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>135769046</v>
       </c>
       <c r="B89" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>135769048</v>
       </c>
       <c r="B90" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>135769059</v>
       </c>
       <c r="B91" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>135769063</v>
       </c>
       <c r="B92" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>135769064</v>
       </c>
       <c r="B93" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135769070</v>
       </c>
       <c r="B94" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>135768977</v>
       </c>
       <c r="B95" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>135768982</v>
       </c>
       <c r="B96" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>135768988</v>
       </c>
       <c r="B97" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>135768994</v>
       </c>
       <c r="B98" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>135768996</v>
       </c>
       <c r="B99" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>135769018</v>
       </c>
       <c r="B100" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>135769034</v>
       </c>
       <c r="B101" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>135769074</v>
       </c>
       <c r="B102" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>135534822</v>
       </c>
       <c r="B72" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 32118-2026 artfynd.xlsx
+++ b/artfynd/A 32118-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135801775</v>
       </c>
       <c r="B2" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>135534875</v>
       </c>
       <c r="B68" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
